--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5501.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5501.xlsx
@@ -1388,9 +1388,21 @@
           <t>5501-24-24-FG</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.77</v>
+      </c>
       <c r="D17" t="n">
         <v>1.875</v>
       </c>
+      <c r="E17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.5</v>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>5501-24-24-FG</t>
@@ -1403,12 +1415,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: Y@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-CAD 2026-10-21: Y@HEX, N4@DRIVE, N6@DRIVE, D1@BORE, D2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 5501-24-24-FG (PARTcommunity / CADENAS, Y@HEX=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 5501-24-24-FG (PARTcommunity / CADENAS, Y@HEX=Y, N4@DRIVE=N, N6@DRIVE=N1, D1@BORE=A1D, D2@BORE=A2D; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
